--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.008438437034621818</v>
       </c>
       <c r="C2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>31675970</v>
+        <v>4254038</v>
       </c>
       <c r="L2" t="n">
-        <v>18071718</v>
+        <v>2011521</v>
       </c>
       <c r="M2" t="n">
-        <v>4392118</v>
+        <v>364128</v>
       </c>
       <c r="N2" t="n">
-        <v>218182</v>
+        <v>9603</v>
       </c>
       <c r="O2" t="n">
-        <v>2615398</v>
+        <v>241961</v>
       </c>
       <c r="P2" t="n">
-        <v>1046160</v>
+        <v>118895</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999479055404663</v>
+        <v>0.99984210729599</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8865461945533752</v>
+        <v>0.783602237701416</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7788368463516235</v>
+        <v>0.6246424317359924</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7330901026725769</v>
+        <v>0.5319200754165649</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3661896288394928</v>
+        <v>0.08633306622505188</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7779021263122559</v>
+        <v>0.6050370931625366</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8493123054504395</v>
+        <v>0.6959883570671082</v>
       </c>
       <c r="X2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="AG2" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AH2" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AI2" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563413858413696</v>
+        <v>0.9555707573890686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113937020301819</v>
+        <v>0.9118538498878479</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8584820032119751</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620789766311646</v>
+        <v>0.6613538861274719</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020217657089233</v>
+        <v>0.9020804166793823</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00202340465893989</v>
       </c>
       <c r="C3" t="n">
-        <v>1500</v>
+        <v>739</v>
       </c>
       <c r="D3" t="n">
-        <v>31675970</v>
+        <v>4254038</v>
       </c>
       <c r="E3" t="n">
-        <v>3407697</v>
+        <v>726076</v>
       </c>
       <c r="F3" t="n">
-        <v>56463</v>
+        <v>15302</v>
       </c>
       <c r="G3" t="n">
-        <v>6000</v>
+        <v>1534</v>
       </c>
       <c r="H3" t="n">
-        <v>3473</v>
+        <v>1329</v>
       </c>
       <c r="I3" t="n">
-        <v>186</v>
+        <v>123</v>
       </c>
       <c r="J3" t="n">
-        <v>70114051</v>
+        <v>10015625</v>
       </c>
       <c r="K3" t="n">
-        <v>75102247</v>
+        <v>10155674</v>
       </c>
       <c r="L3" t="n">
-        <v>86287494</v>
+        <v>11833326</v>
       </c>
       <c r="M3" t="n">
-        <v>106175201</v>
+        <v>15072625</v>
       </c>
       <c r="N3" t="n">
-        <v>113305110</v>
+        <v>16138507</v>
       </c>
       <c r="O3" t="n">
-        <v>109994234</v>
+        <v>15661208</v>
       </c>
       <c r="P3" t="n">
-        <v>112768055</v>
+        <v>16084159</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9011325240135193</v>
+        <v>0.8509538173675537</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7895733714103699</v>
+        <v>0.6118659973144531</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6723098158836365</v>
+        <v>0.3887976109981537</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3493958711624146</v>
+        <v>0.1073392629623413</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7333754301071167</v>
+        <v>0.4740225076675415</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7729111909866333</v>
+        <v>0.6144222021102905</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="Z3" t="n">
-        <v>1384204</v>
+        <v>196812</v>
       </c>
       <c r="AA3" t="n">
-        <v>59560</v>
+        <v>8425</v>
       </c>
       <c r="AB3" t="n">
-        <v>47621</v>
+        <v>6828</v>
       </c>
       <c r="AC3" t="n">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70116354</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>77619300</v>
+        <v>11107886</v>
       </c>
       <c r="AG3" t="n">
-        <v>89394449</v>
+        <v>12753027</v>
       </c>
       <c r="AH3" t="n">
-        <v>106848837</v>
+        <v>15260727</v>
       </c>
       <c r="AI3" t="n">
-        <v>113471912</v>
+        <v>16209880</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110391725</v>
+        <v>15769225</v>
       </c>
       <c r="AK3" t="n">
-        <v>112860888</v>
+        <v>16122838</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575594067573547</v>
+        <v>0.9575715065002441</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099474549293518</v>
+        <v>0.9095625281333923</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574531674385071</v>
+        <v>0.8570923805236816</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6615032553672791</v>
+        <v>0.6604667901992798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015399217605591</v>
+        <v>0.9011915326118469</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03193072151668488</v>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>3806204</v>
+        <v>1089036</v>
       </c>
       <c r="E4" t="n">
-        <v>18071718</v>
+        <v>2011521</v>
       </c>
       <c r="F4" t="n">
-        <v>890298</v>
+        <v>149939</v>
       </c>
       <c r="G4" t="n">
-        <v>40329</v>
+        <v>11967</v>
       </c>
       <c r="H4" t="n">
-        <v>72128</v>
+        <v>21729</v>
       </c>
       <c r="I4" t="n">
-        <v>7234</v>
+        <v>3291</v>
       </c>
       <c r="J4" t="n">
-        <v>2303</v>
+        <v>997</v>
       </c>
       <c r="K4" t="n">
-        <v>4053664</v>
+        <v>1174785</v>
       </c>
       <c r="L4" t="n">
-        <v>5131753</v>
+        <v>1208755</v>
       </c>
       <c r="M4" t="n">
-        <v>1599121</v>
+        <v>320426</v>
       </c>
       <c r="N4" t="n">
-        <v>377635</v>
+        <v>101629</v>
       </c>
       <c r="O4" t="n">
-        <v>746719</v>
+        <v>157950</v>
       </c>
       <c r="P4" t="n">
-        <v>185613</v>
+        <v>51934</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999739527702332</v>
+        <v>0.9999210238456726</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8937798142433167</v>
+        <v>0.8158904314041138</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7841683626174927</v>
+        <v>0.6181882619857788</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7013856768608093</v>
+        <v>0.4492348730564117</v>
       </c>
       <c r="U4" t="n">
-        <v>0.357595682144165</v>
+        <v>0.09569697082042694</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7549828290939331</v>
+        <v>0.5315761566162109</v>
       </c>
       <c r="W4" t="n">
-        <v>0.809312641620636</v>
+        <v>0.6526667475700378</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1434717</v>
+        <v>207948</v>
       </c>
       <c r="Z4" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AA4" t="n">
-        <v>579437</v>
+        <v>82633</v>
       </c>
       <c r="AB4" t="n">
-        <v>38501</v>
+        <v>5536</v>
       </c>
       <c r="AC4" t="n">
-        <v>7988</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1536611</v>
+        <v>222573</v>
       </c>
       <c r="AG4" t="n">
-        <v>2024798</v>
+        <v>289054</v>
       </c>
       <c r="AH4" t="n">
-        <v>925485</v>
+        <v>132324</v>
       </c>
       <c r="AI4" t="n">
-        <v>210833</v>
+        <v>30256</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349228</v>
+        <v>49933</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569499492645264</v>
+        <v>0.9565700888633728</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106699824333191</v>
+        <v>0.9107067584991455</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578310608863831</v>
+        <v>0.8577865958213806</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617910265922546</v>
+        <v>0.6609100103378296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017807841300964</v>
+        <v>0.9016357064247131</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>396</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>164287</v>
+        <v>61510</v>
       </c>
       <c r="E5" t="n">
-        <v>1464560</v>
+        <v>399264</v>
       </c>
       <c r="F5" t="n">
-        <v>4392118</v>
+        <v>364128</v>
       </c>
       <c r="G5" t="n">
-        <v>128682</v>
+        <v>29741</v>
       </c>
       <c r="H5" t="n">
-        <v>350465</v>
+        <v>70176</v>
       </c>
       <c r="I5" t="n">
-        <v>32370</v>
+        <v>11695</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3475319</v>
+        <v>745103</v>
       </c>
       <c r="L5" t="n">
-        <v>4816235</v>
+        <v>1275998</v>
       </c>
       <c r="M5" t="n">
-        <v>2140760</v>
+        <v>572421</v>
       </c>
       <c r="N5" t="n">
-        <v>406273</v>
+        <v>79861</v>
       </c>
       <c r="O5" t="n">
-        <v>950849</v>
+        <v>268481</v>
       </c>
       <c r="P5" t="n">
-        <v>307372</v>
+        <v>74612</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999798536300659</v>
+        <v>0.99993896484375</v>
       </c>
       <c r="R5" t="n">
-        <v>0.934133768081665</v>
+        <v>0.8824289441108704</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9129714369773865</v>
+        <v>0.847837507724762</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9672821760177612</v>
+        <v>0.9453234076499939</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9931420683860779</v>
+        <v>0.9888858199119568</v>
       </c>
       <c r="V5" t="n">
-        <v>0.985149085521698</v>
+        <v>0.9738860130310059</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9956871867179871</v>
+        <v>0.9922505021095276</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56186</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>596891</v>
+        <v>86001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AB5" t="n">
-        <v>69704</v>
+        <v>9990</v>
       </c>
       <c r="AC5" t="n">
-        <v>204029</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1491842</v>
+        <v>212106</v>
       </c>
       <c r="AG5" t="n">
-        <v>2061119</v>
+        <v>297315</v>
       </c>
       <c r="AH5" t="n">
-        <v>931241</v>
+        <v>133840</v>
       </c>
       <c r="AI5" t="n">
-        <v>211376</v>
+        <v>30376</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351133</v>
+        <v>50436</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735060334205627</v>
+        <v>0.9733809232711792</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642549753189087</v>
+        <v>0.9640916585922241</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837567210197449</v>
+        <v>0.9837005138397217</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963063597679138</v>
+        <v>0.9962869882583618</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938730001449585</v>
+        <v>0.9938535690307617</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983745217323303</v>
+        <v>0.9983724355697632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="D6" t="n">
-        <v>77307</v>
+        <v>20254</v>
       </c>
       <c r="E6" t="n">
-        <v>119736</v>
+        <v>22621</v>
       </c>
       <c r="F6" t="n">
-        <v>143588</v>
+        <v>26161</v>
       </c>
       <c r="G6" t="n">
-        <v>218182</v>
+        <v>9603</v>
       </c>
       <c r="H6" t="n">
-        <v>59834</v>
+        <v>9130</v>
       </c>
       <c r="I6" t="n">
-        <v>5644</v>
+        <v>1609</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45337</v>
+        <v>6558</v>
       </c>
       <c r="Z6" t="n">
-        <v>37466</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>76329</v>
+        <v>10994</v>
       </c>
       <c r="AB6" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AC6" t="n">
-        <v>48877</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>5523</v>
+        <v>3810</v>
       </c>
       <c r="E7" t="n">
-        <v>131158</v>
+        <v>56429</v>
       </c>
       <c r="F7" t="n">
-        <v>484831</v>
+        <v>120072</v>
       </c>
       <c r="G7" t="n">
-        <v>189118</v>
+        <v>52934</v>
       </c>
       <c r="H7" t="n">
-        <v>2615398</v>
+        <v>241961</v>
       </c>
       <c r="I7" t="n">
-        <v>140179</v>
+        <v>35216</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5670</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207844</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53148</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>175</v>
       </c>
       <c r="E8" t="n">
-        <v>8602</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="n">
-        <v>23941</v>
+        <v>8952</v>
       </c>
       <c r="G8" t="n">
-        <v>13506</v>
+        <v>5453</v>
       </c>
       <c r="H8" t="n">
-        <v>260819</v>
+        <v>55586</v>
       </c>
       <c r="I8" t="n">
-        <v>1046160</v>
+        <v>118895</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
